--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.620131969451904</v>
+        <v>1.643066167831421</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999993011976304</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.929586410522461</v>
+        <v>1.933768033981323</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999995124314008</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.620131969451904</v>
+        <v>1.643066167831421</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999993011976304</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.929586410522461</v>
+        <v>1.933768033981323</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999995124314008</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.643066167831421</v>
+        <v>2.385154962539673</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999993011976304</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999996436613721</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01176360860315794</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009252170390775166</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.933768033981323</v>
+        <v>2.595376253128052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999995124314008</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999996436613721</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01176360860315794</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009252170390775166</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.643066167831421</v>
+        <v>2.385154962539673</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999993011976304</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999996436613721</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01176360860315794</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009252170390775166</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.933768033981323</v>
+        <v>2.595376253128052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999995124314008</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999996436613721</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01176360860315794</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009252170390775166</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.385154962539673</v>
+        <v>2.441129922866821</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9919591707630674</v>
+        <v>0.8737393357673123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.8826418409631959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.625469537425023</v>
+        <v>685.9973785244678</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102047839255723</v>
+        <v>439.4143072982781</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.595376253128052</v>
+        <v>2.698471784591675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922542316820335</v>
+        <v>0.8710781596729227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.8826418409631959</v>
       </c>
       <c r="G3" t="n">
-        <v>1.625469537425023</v>
+        <v>685.9973785244678</v>
       </c>
       <c r="H3" t="n">
-        <v>1.102047839255723</v>
+        <v>439.4143072982781</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.423628568649292</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8766648332505442</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8836444953813559</v>
+      </c>
+      <c r="G4" t="n">
+        <v>683.0606687180078</v>
+      </c>
+      <c r="H4" t="n">
+        <v>449.9791831660115</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.385154962539673</v>
+        <v>2.441129922866821</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9919591707630674</v>
+        <v>0.8737393357673123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.8826418409631959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.625469537425023</v>
+        <v>685.9973785244678</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102047839255723</v>
+        <v>439.4143072982781</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.595376253128052</v>
+        <v>2.698471784591675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922542316820335</v>
+        <v>0.8710781596729227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.8826418409631959</v>
       </c>
       <c r="G3" t="n">
-        <v>1.625469537425023</v>
+        <v>685.9973785244678</v>
       </c>
       <c r="H3" t="n">
-        <v>1.102047839255723</v>
+        <v>439.4143072982781</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.423628568649292</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8766648332505442</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8836444953813559</v>
+      </c>
+      <c r="G4" t="n">
+        <v>683.0606687180078</v>
+      </c>
+      <c r="H4" t="n">
+        <v>449.9791831660115</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.441129922866821</v>
+        <v>69.19719624519348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8737393357673123</v>
+        <v>0.9455909458238664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8826418409631959</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G2" t="n">
-        <v>685.9973785244678</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H2" t="n">
-        <v>439.4143072982781</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.698471784591675</v>
+        <v>91.62624907493591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8710781596729227</v>
+        <v>0.9484161735684404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8826418409631959</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G3" t="n">
-        <v>685.9973785244678</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H3" t="n">
-        <v>439.4143072982781</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.423628568649292</v>
+        <v>179.7915933132172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8766648332505442</v>
+        <v>0.9509164386453003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8836444953813559</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G4" t="n">
-        <v>683.0606687180078</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H4" t="n">
-        <v>449.9791831660115</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.441129922866821</v>
+        <v>69.19719624519348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8737393357673123</v>
+        <v>0.9455909458238664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8826418409631959</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G2" t="n">
-        <v>685.9973785244678</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H2" t="n">
-        <v>439.4143072982781</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.698471784591675</v>
+        <v>91.62624907493591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8710781596729227</v>
+        <v>0.9484161735684404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8826418409631959</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G3" t="n">
-        <v>685.9973785244678</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H3" t="n">
-        <v>439.4143072982781</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.423628568649292</v>
+        <v>179.7915933132172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8766648332505442</v>
+        <v>0.9509164386453003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8836444953813559</v>
+        <v>0.9510117078430874</v>
       </c>
       <c r="G4" t="n">
-        <v>683.0606687180078</v>
+        <v>39.38571342275206</v>
       </c>
       <c r="H4" t="n">
-        <v>449.9791831660115</v>
+        <v>24.1584622920368</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>69.19719624519348</v>
+        <v>1.393115043640137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9455909458238664</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9510117078430874</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>39.38571342275206</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>24.1584622920368</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>91.62624907493591</v>
+        <v>1.58259129524231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9484161735684404</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9510117078430874</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>39.38571342275206</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>24.1584622920368</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>179.7915933132172</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9509164386453003</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9510117078430874</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.38571342275206</v>
-      </c>
-      <c r="H4" t="n">
-        <v>24.1584622920368</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>69.19719624519348</v>
+        <v>1.393115043640137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9455909458238664</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9510117078430874</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>39.38571342275206</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>24.1584622920368</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>91.62624907493591</v>
+        <v>1.58259129524231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9484161735684404</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9510117078430874</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>39.38571342275206</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>24.1584622920368</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>179.7915933132172</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9509164386453003</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9510117078430874</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.38571342275206</v>
-      </c>
-      <c r="H4" t="n">
-        <v>24.1584622920368</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393115043640137</v>
+        <v>1.451559066772461</v>
       </c>
       <c r="E2" t="n">
         <v>0.9919591707630674</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.58259129524231</v>
+        <v>1.595117807388306</v>
       </c>
       <c r="E3" t="n">
         <v>0.9922542316820335</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393115043640137</v>
+        <v>1.451559066772461</v>
       </c>
       <c r="E2" t="n">
         <v>0.9919591707630674</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.58259129524231</v>
+        <v>1.595117807388306</v>
       </c>
       <c r="E3" t="n">
         <v>0.9922542316820335</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.451559066772461</v>
+        <v>1.166559934616089</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9919591707630674</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>1.625469537425023</v>
+        <v>1.723721485354506</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102047839255723</v>
+        <v>1.110294250898929</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.595117807388306</v>
+        <v>1.53929591178894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922542316820335</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>1.625469537425023</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>1.102047839255723</v>
+        <v>1.068923415563533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.451559066772461</v>
+        <v>1.166559934616089</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9919591707630674</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>1.625469537425023</v>
+        <v>1.723721485354506</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102047839255723</v>
+        <v>1.110294250898929</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.595117807388306</v>
+        <v>1.53929591178894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922542316820335</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9931963895337861</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>1.625469537425023</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>1.102047839255723</v>
+        <v>1.068923415563533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.166559934616089</v>
+        <v>0.85890793800354</v>
       </c>
       <c r="E2" t="n">
         <v>0.9911019302061744</v>
@@ -500,10 +500,10 @@
         <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354506</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898929</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53929591178894</v>
+        <v>1.197846174240112</v>
       </c>
       <c r="E3" t="n">
         <v>0.9916725619279564</v>
@@ -538,7 +538,7 @@
         <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563533</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.166559934616089</v>
+        <v>0.85890793800354</v>
       </c>
       <c r="E2" t="n">
         <v>0.9911019302061744</v>
@@ -631,10 +631,10 @@
         <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354506</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898929</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53929591178894</v>
+        <v>1.197846174240112</v>
       </c>
       <c r="E3" t="n">
         <v>0.9916725619279564</v>
@@ -669,7 +669,7 @@
         <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563533</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.85890793800354</v>
+        <v>64.51921892166138</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9451094020818683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.197846174240112</v>
+        <v>119.5911319255829</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.9477025989384391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.85890793800354</v>
+        <v>64.51921892166138</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9451094020818683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.197846174240112</v>
+        <v>119.5911319255829</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.9477025989384391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>64.51921892166138</v>
+        <v>8.325294256210327</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9451094020818683</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63662984415944</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H2" t="n">
-        <v>23.90459760874549</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>119.5911319255829</v>
+        <v>11.31248903274536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9477025989384391</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G3" t="n">
-        <v>39.63662984415944</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H3" t="n">
-        <v>23.90459760874549</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>64.51921892166138</v>
+        <v>8.325294256210327</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9451094020818683</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63662984415944</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H2" t="n">
-        <v>23.90459760874549</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>119.5911319255829</v>
+        <v>11.31248903274536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9477025989384391</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G3" t="n">
-        <v>39.63662984415944</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H3" t="n">
-        <v>23.90459760874549</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.325294256210327</v>
+        <v>138.7347369194031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4623585754058815</v>
+        <v>0.4742039714755084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.5480245530595298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5918812206686007</v>
+        <v>67.25295138365956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4270981493479949</v>
+        <v>31.38330002219408</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.31248903274536</v>
+        <v>176.5487792491913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48977812589358</v>
+        <v>0.5006287526437336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.5478088376009014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5918812206686007</v>
+        <v>67.26899846183061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4270981493479949</v>
+        <v>31.30699612414678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.325294256210327</v>
+        <v>138.7347369194031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4623585754058815</v>
+        <v>0.4742039714755084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.5480245530595298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5918812206686007</v>
+        <v>67.25295138365956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4270981493479949</v>
+        <v>31.38330002219408</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.31248903274536</v>
+        <v>176.5487792491913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48977812589358</v>
+        <v>0.5006287526437336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.5478088376009014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5918812206686007</v>
+        <v>67.26899846183061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4270981493479949</v>
+        <v>31.30699612414678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>138.7347369194031</v>
+        <v>1.444255590438843</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>67.25295138365956</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38330002219408</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>176.5487792491913</v>
+        <v>1.722037076950073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26899846183061</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>31.30699612414678</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.804654598236084</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>138.7347369194031</v>
+        <v>1.444255590438843</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>67.25295138365956</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38330002219408</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>176.5487792491913</v>
+        <v>1.722037076950073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26899846183061</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>31.30699612414678</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.804654598236084</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.444255590438843</v>
+        <v>35.37915015220642</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9451094020818683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.722037076950073</v>
+        <v>50.37099456787109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.9477025989384391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.804654598236084</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.444255590438843</v>
+        <v>35.37915015220642</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9451094020818683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.722037076950073</v>
+        <v>50.37099456787109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.9477025989384391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9503855355387685</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>39.63662984415944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>23.90459760874549</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.804654598236084</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37915015220642</v>
+        <v>407.0889031887054</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9451094020818683</v>
+        <v>0.999963839089749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.9999787651075426</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63662984415944</v>
+        <v>0.04423790566095208</v>
       </c>
       <c r="H2" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01322032863127662</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.37099456787109</v>
+        <v>669.6786866188049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9477025989384391</v>
+        <v>0.999970790667121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.9999787193001012</v>
       </c>
       <c r="G3" t="n">
-        <v>39.63662984415944</v>
+        <v>0.04428559447337719</v>
       </c>
       <c r="H3" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01312509334958275</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37915015220642</v>
+        <v>407.0889031887054</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9451094020818683</v>
+        <v>0.999963839089749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.9999787651075426</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63662984415944</v>
+        <v>0.04423790566095208</v>
       </c>
       <c r="H2" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01322032863127662</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.37099456787109</v>
+        <v>669.6786866188049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9477025989384391</v>
+        <v>0.999970790667121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9503855355387685</v>
+        <v>0.9999787193001012</v>
       </c>
       <c r="G3" t="n">
-        <v>39.63662984415944</v>
+        <v>0.04428559447337719</v>
       </c>
       <c r="H3" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01312509334958275</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>407.0889031887054</v>
+        <v>138.0690364837646</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999963839089749</v>
+        <v>0.4742039714755084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999787651075426</v>
+        <v>0.5480245530595298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04423790566095208</v>
+        <v>67.25295138365956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01322032863127662</v>
+        <v>31.38330002219408</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>669.6786866188049</v>
+        <v>175.5471067428589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.999970790667121</v>
+        <v>0.5006287526437336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999787193001012</v>
+        <v>0.5478088376009014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04428559447337719</v>
+        <v>67.26899846183061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01312509334958275</v>
+        <v>31.30699612414678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>407.0889031887054</v>
+        <v>138.0690364837646</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999963839089749</v>
+        <v>0.4742039714755084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999787651075426</v>
+        <v>0.5480245530595298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04423790566095208</v>
+        <v>67.25295138365956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01322032863127662</v>
+        <v>31.38330002219408</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>669.6786866188049</v>
+        <v>175.5471067428589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.999970790667121</v>
+        <v>0.5006287526437336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999787193001012</v>
+        <v>0.5478088376009014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04428559447337719</v>
+        <v>67.26899846183061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01312509334958275</v>
+        <v>31.30699612414678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>138.0690364837646</v>
+        <v>359.0611598491669</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9143654286374646</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.929790484223216</v>
       </c>
       <c r="G2" t="n">
-        <v>67.25295138365956</v>
+        <v>8.989816532636402</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38330002219408</v>
+        <v>5.108558655758215</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.5471067428589</v>
+        <v>475.1110761165619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9195783641133068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9298079132741046</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26899846183061</v>
+        <v>8.988700631940874</v>
       </c>
       <c r="H3" t="n">
-        <v>31.30699612414678</v>
+        <v>5.102076726523771</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>138.0690364837646</v>
+        <v>359.0611598491669</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9143654286374646</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.929790484223216</v>
       </c>
       <c r="G2" t="n">
-        <v>67.25295138365956</v>
+        <v>8.989816532636402</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38330002219408</v>
+        <v>5.108558655758215</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.5471067428589</v>
+        <v>475.1110761165619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9195783641133068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9298079132741046</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26899846183061</v>
+        <v>8.988700631940874</v>
       </c>
       <c r="H3" t="n">
-        <v>31.30699612414678</v>
+        <v>5.102076726523771</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>359.0611598491669</v>
+        <v>11.00290584564209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9143654286374646</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.929790484223216</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G2" t="n">
-        <v>8.989816532636402</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H2" t="n">
-        <v>5.108558655758215</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>475.1110761165619</v>
+        <v>13.14061999320984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9195783641133068</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9298079132741046</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G3" t="n">
-        <v>8.988700631940874</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H3" t="n">
-        <v>5.102076726523771</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>359.0611598491669</v>
+        <v>11.00290584564209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9143654286374646</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.929790484223216</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G2" t="n">
-        <v>8.989816532636402</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H2" t="n">
-        <v>5.108558655758215</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>475.1110761165619</v>
+        <v>13.14061999320984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9195783641133068</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9298079132741046</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="G3" t="n">
-        <v>8.988700631940874</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="H3" t="n">
-        <v>5.102076726523771</v>
+        <v>0.4270981493479949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.00290584564209</v>
+        <v>1.201832294464111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4623585754058815</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5918812206686007</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4270981493479949</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.14061999320984</v>
+        <v>1.590012073516846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48977812589358</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5918812206686007</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4270981493479949</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.500810146331787</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.00290584564209</v>
+        <v>1.201832294464111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4623585754058815</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5918812206686007</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4270981493479949</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.14061999320984</v>
+        <v>1.590012073516846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48977812589358</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5476623229282194</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5918812206686007</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4270981493479949</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.500810146331787</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.201832294464111</v>
+        <v>1.199609279632568</v>
       </c>
       <c r="E2" t="n">
         <v>0.9911019302061744</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.590012073516846</v>
+        <v>1.537432909011841</v>
       </c>
       <c r="E3" t="n">
         <v>0.9916725619279564</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.500810146331787</v>
+        <v>2.334842205047607</v>
       </c>
       <c r="E4" t="n">
         <v>0.991650272801923</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.201832294464111</v>
+        <v>1.199609279632568</v>
       </c>
       <c r="E2" t="n">
         <v>0.9911019302061744</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.590012073516846</v>
+        <v>1.537432909011841</v>
       </c>
       <c r="E3" t="n">
         <v>0.9916725619279564</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.500810146331787</v>
+        <v>2.334842205047607</v>
       </c>
       <c r="E4" t="n">
         <v>0.991650272801923</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.199609279632568</v>
+        <v>24.79525923728943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9231975057768378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9288018973917292</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>35.58712489594088</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>21.54101354188551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.537432909011841</v>
+        <v>34.34850692749023</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.929710237901235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9288018973917292</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>35.58712489594088</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>21.54101354188551</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.334842205047607</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.199609279632568</v>
+        <v>24.79525923728943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911019302061744</v>
+        <v>0.9231975057768378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9923490394853252</v>
+        <v>0.9288018973917292</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723721485354504</v>
+        <v>35.58712489594088</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110294250898904</v>
+        <v>21.54101354188551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.537432909011841</v>
+        <v>34.34850692749023</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9916725619279564</v>
+        <v>0.929710237901235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9927500166340855</v>
+        <v>0.9288018973917292</v>
       </c>
       <c r="G3" t="n">
-        <v>1.677944607223844</v>
+        <v>35.58712489594088</v>
       </c>
       <c r="H3" t="n">
-        <v>1.068923415563526</v>
+        <v>21.54101354188551</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.334842205047607</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79525923728943</v>
+        <v>67.2276451587677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9231975057768378</v>
+        <v>0.9317507467241954</v>
       </c>
       <c r="F2" t="n">
         <v>0.9288018973917292</v>
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>34.34850692749023</v>
+        <v>121.8825795650482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.929710237901235</v>
+        <v>0.9319565654152878</v>
       </c>
       <c r="F3" t="n">
         <v>0.9288018973917292</v>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79525923728943</v>
+        <v>67.2276451587677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9231975057768378</v>
+        <v>0.9317507467241954</v>
       </c>
       <c r="F2" t="n">
         <v>0.9288018973917292</v>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>34.34850692749023</v>
+        <v>121.8825795650482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.929710237901235</v>
+        <v>0.9319565654152878</v>
       </c>
       <c r="F3" t="n">
         <v>0.9288018973917292</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.2276451587677</v>
+        <v>1.215555906295776</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9317507467241954</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9288018973917292</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58712489594088</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>21.54101354188551</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -523,24 +523,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>121.8825795650482</v>
+        <v>1.493859052658081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9319565654152878</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9288018973917292</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>35.58712489594088</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>21.54101354188551</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.197186708450317</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.2276451587677</v>
+        <v>1.215555906295776</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9317507467241954</v>
+        <v>0.9911019302061744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9288018973917292</v>
+        <v>0.9923490394853252</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58712489594088</v>
+        <v>1.723721485354504</v>
       </c>
       <c r="H2" t="n">
-        <v>21.54101354188551</v>
+        <v>1.110294250898904</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -654,24 +689,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>121.8825795650482</v>
+        <v>1.493859052658081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9319565654152878</v>
+        <v>0.9916725619279564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9288018973917292</v>
+        <v>0.9927500166340855</v>
       </c>
       <c r="G3" t="n">
-        <v>35.58712489594088</v>
+        <v>1.677944607223844</v>
       </c>
       <c r="H3" t="n">
-        <v>21.54101354188551</v>
+        <v>1.068923415563526</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.197186708450317</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
